--- a/отчеты для СН/Расчет времени.xlsx
+++ b/отчеты для СН/Расчет времени.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\отчеты для СН\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066930C4-79BA-4472-94E6-75CC10D1EAFF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41132798-819C-41DA-AE89-BBA5664D644D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2DB1739C-891E-48B0-A6F8-D78828AD9D70}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>Перенос в бланк заказа</t>
   </si>
@@ -91,14 +91,27 @@
   </si>
   <si>
     <t>Добавил Останкино сыры.</t>
+  </si>
+  <si>
+    <t>тонн</t>
+  </si>
+  <si>
+    <t>тонн в машине</t>
+  </si>
+  <si>
+    <t>кол-во машин</t>
+  </si>
+  <si>
+    <t>данные за пол месяца</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.??"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -371,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -472,6 +485,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -789,7 +814,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" customWidth="1"/>
@@ -799,9 +824,13 @@
     <col min="8" max="10" width="9" customWidth="1"/>
     <col min="11" max="12" width="8.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" customWidth="1"/>
+    <col min="15" max="15" width="8" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" style="35" customWidth="1"/>
+    <col min="17" max="17" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -817,7 +846,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="32" t="s">
         <v>2</v>
@@ -849,7 +878,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
       <c r="C3" s="33"/>
       <c r="D3" s="22" t="s">
@@ -874,10 +903,17 @@
         <v>5</v>
       </c>
       <c r="M3" s="33"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>1</v>
       </c>
@@ -920,10 +956,18 @@
         <f>H4*J4</f>
         <v>180</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="1">
+        <v>134.69999999999999</v>
+      </c>
+      <c r="O4" s="1">
+        <v>17</v>
+      </c>
+      <c r="P4" s="35">
+        <f>N4/O4</f>
+        <v>7.9235294117647053</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <v>2</v>
       </c>
@@ -966,10 +1010,18 @@
         <f t="shared" ref="M5:M8" si="2">H5*J5</f>
         <v>160</v>
       </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N5" s="1">
+        <v>642.20000000000005</v>
+      </c>
+      <c r="O5" s="1">
+        <v>18</v>
+      </c>
+      <c r="P5" s="35">
+        <f t="shared" ref="P5:P8" si="3">N5/O5</f>
+        <v>35.677777777777777</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
         <v>3</v>
       </c>
@@ -1001,21 +1053,29 @@
         <v>16</v>
       </c>
       <c r="K6" s="7">
-        <f t="shared" ref="K6" si="3">($C6+D6+F6+$H6)*$I6</f>
+        <f t="shared" ref="K6" si="4">($C6+D6+F6+$H6)*$I6</f>
         <v>1040</v>
       </c>
       <c r="L6" s="8">
-        <f t="shared" ref="L6" si="4">($C6+E6+G6+$H6)*$I6</f>
+        <f t="shared" ref="L6" si="5">($C6+E6+G6+$H6)*$I6</f>
         <v>1520</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" ref="M6" si="5">H6*J6</f>
+        <f t="shared" ref="M6" si="6">H6*J6</f>
         <v>80</v>
       </c>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N6" s="1">
+        <v>131.6</v>
+      </c>
+      <c r="O6" s="1">
+        <v>11</v>
+      </c>
+      <c r="P6" s="35">
+        <f t="shared" si="3"/>
+        <v>11.963636363636363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>4</v>
       </c>
@@ -1047,21 +1107,29 @@
         <v>16</v>
       </c>
       <c r="K7" s="7">
-        <f t="shared" ref="K7" si="6">($C7+D7+F7+$H7)*$I7</f>
+        <f t="shared" ref="K7" si="7">($C7+D7+F7+$H7)*$I7</f>
         <v>900</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" ref="L7" si="7">($C7+E7+G7+$H7)*$I7</f>
+        <f t="shared" ref="L7" si="8">($C7+E7+G7+$H7)*$I7</f>
         <v>1300</v>
       </c>
       <c r="M7" s="6">
-        <f t="shared" ref="M7" si="8">H7*J7</f>
+        <f t="shared" ref="M7" si="9">H7*J7</f>
         <v>80</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="1">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="O7" s="1">
+        <v>16</v>
+      </c>
+      <c r="P7" s="35">
+        <f t="shared" si="3"/>
+        <v>1.0874999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>5</v>
       </c>
@@ -1087,27 +1155,38 @@
         <v>5</v>
       </c>
       <c r="I8" s="27">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J8" s="27">
         <v>16</v>
       </c>
       <c r="K8" s="10">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="L8" s="11">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="M8" s="9">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N8" s="37">
+        <v>3.3</v>
+      </c>
+      <c r="O8" s="37">
+        <v>11</v>
+      </c>
+      <c r="P8" s="38">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q8" s="39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1121,11 +1200,11 @@
       </c>
       <c r="K9" s="14">
         <f>SUM(K4:K8)</f>
-        <v>6060</v>
+        <v>6180</v>
       </c>
       <c r="L9" s="14">
         <f>SUM(L4:L8)</f>
-        <v>8860</v>
+        <v>9040</v>
       </c>
       <c r="M9" s="14">
         <f>SUM(M4:M8)</f>
@@ -1134,7 +1213,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" s="13"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -1148,20 +1227,20 @@
       </c>
       <c r="K10" s="18">
         <f>K9/60</f>
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L10" s="18">
-        <f t="shared" ref="L10:M10" si="9">L9/60</f>
-        <v>147.66666666666666</v>
+        <f t="shared" ref="L10:M10" si="10">L9/60</f>
+        <v>150.66666666666666</v>
       </c>
       <c r="M10" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.6666666666666661</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -1175,17 +1254,17 @@
       </c>
       <c r="K11" s="17">
         <f>(K9+$M$9)/60</f>
-        <v>110.66666666666667</v>
+        <v>112.66666666666667</v>
       </c>
       <c r="L11" s="17">
         <f>(L9+$M$9)/60</f>
-        <v>157.33333333333334</v>
+        <v>160.33333333333334</v>
       </c>
       <c r="M11" s="14"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12" s="13"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1201,7 +1280,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -1217,7 +1296,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14" s="30" t="s">
         <v>18</v>
       </c>
@@ -1233,7 +1312,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="30"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
         <v>19</v>
       </c>
